--- a/output/11_北塩原村第10期_図表データ管理台帳.xlsx
+++ b/output/11_北塩原村第10期_図表データ管理台帳.xlsx
@@ -7805,7 +7805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>重複23系列／図のみ30系列／食い違い0系列</t>
+          <t>正本を参照30系列／図の間の重なり2系列／じか書き0系列／図のみ21系列／食い違い0系列</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -8258,24 +8258,74 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>素案の表に数値がじか書きされていないこと</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>02シートのじか書き == 0</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>0系列（正本を参照しているもの30系列）</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>正本を参照していると称した系列が、実際に素案の表と同じ数値を持つこと</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>LINKED の全件が02シートで突き合わさる</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>30／30系列</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>台帳の上で直された数値が、正本に取り込まれていること</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>台帳の値 == data_zuhyo.py の値</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>取り込まれていない値0件</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8317,7 +8367,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>図の数値と同じ並びが計画素案の表にもないかを機械で探しています。「同じ数値が表にもある」図は、数値を直すときに表の側も直す必要があります。対応する表がない図は、図だけが数値を持っています。</t>
+          <t>図の数値と同じ並びが計画素案の表にもないかを機械で探しています。区分の名で突き合わせており、和暦と西暦の違いは寄せています。「素案の表はこの系列を参照しています」の行は、表が数値を持たず本表から引いているため、ここで直せば図と表の両方が変わります。「★表に数値がじか書きされています」の行があれば、同じ数値が2か所にあり片方だけが直る恐れがあります。対応する表がない図は、図だけが数値を持っています。</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8431,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+          <t>図と図が同じ数値を持ちます（図2-3・図2-4の平成22年（2010年）と重なる）。素案の表は重なり先の図を参照しています</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8461,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+          <t>図と図が同じ数値を持ちます（図2-3・図2-4の令和7年（2025年）と重なる）。素案の表は重なり先の図を参照しています</t>
         </is>
       </c>
     </row>
@@ -8431,19 +8481,17 @@
           <t>北塩原村</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D8" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-1　年 / 北塩原村 / 福島県 / 全国 / 県との差（列：北塩原村）</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8463,19 +8511,17 @@
           <t>福島県</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D9" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-1　年 / 北塩原村 / 福島県 / 全国 / 県との差（列：福島県）</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8495,19 +8541,17 @@
           <t>全国</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D10" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-1　年 / 北塩原村 / 福島県 / 全国 / 県との差（列：全国）</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8527,19 +8571,17 @@
           <t>15歳未満</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D11" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：15歳未満）</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8559,19 +8601,17 @@
           <t>15〜64歳</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D12" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：生産年齢人口）</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8591,19 +8631,17 @@
           <t>65歳以上</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D13" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第5章 5-11　 / 令和7年 / 令和12年 / 令和17年 / 令和22年（行：高齢者人口）</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8623,19 +8661,17 @@
           <t>総人口</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D14" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：総人口）</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8655,19 +8691,17 @@
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D15" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：65〜74歳）</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8687,19 +8721,17 @@
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D16" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：75歳以上）</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8727,9 +8759,9 @@
           <t>第2章 2-3　時点 / 北塩原村 / 福島県 / 全国（列：北塩原村）</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8757,9 +8789,9 @@
           <t>第2章 2-3　時点 / 北塩原村 / 福島県 / 全国（列：福島県）</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8787,9 +8819,9 @@
           <t>第2章 2-3　時点 / 北塩原村 / 福島県 / 全国（列：全国）</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8817,9 +8849,9 @@
           <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要支援1）</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8847,9 +8879,9 @@
           <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要支援2）</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8877,9 +8909,9 @@
           <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護1）</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8907,9 +8939,9 @@
           <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護2）</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8937,9 +8969,9 @@
           <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護3）</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8967,9 +8999,9 @@
           <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護4）</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -8997,9 +9029,9 @@
           <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護5）</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9091,9 +9123,9 @@
           <t>第2章 2-4　年度 / 北塩原村 / 福島県 / 全国 / 県との差（列：北塩原村）</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9121,9 +9153,9 @@
           <t>第2章 2-4　年度 / 北塩原村 / 福島県 / 全国 / 県との差（列：福島県）</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9151,9 +9183,9 @@
           <t>第2章 2-4　年度 / 北塩原村 / 福島県 / 全国 / 県との差（列：全国）</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9341,9 +9373,9 @@
           <t>第2章 2-4　区分 / 平成29年度 / 令和7年度 / 増減 / 増減率 / 令和7年度の構（列：平成29年度）</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9371,9 +9403,9 @@
           <t>第2章 2-4　区分 / 平成29年度 / 令和7年度 / 増減 / 増減率 / 令和7年度の構（列：令和7年度）</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9401,9 +9433,9 @@
           <t>第2章 2-5　年度 / 居住系定員（認知症GH） / 通所系定員（通所介護） / 1人あたり定（列：1人あたり定員（通所系））</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9431,9 +9463,9 @@
           <t>第2章 2-5　年度 / 居住系定員（認知症GH） / 通所系定員（通所介護） / 1人あたり定（列：1人あたり定員（居住系））</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9621,9 +9653,9 @@
           <t>第2章 2-9　年度 / 計画値 / 決算額 / 差（列：決算額）</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9939,9 +9971,9 @@
           <t>第2章 2-8　 / 令和6年度 / 令和7年度 / 令和8年度（行：合計（800点））</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9969,9 +10001,9 @@
           <t>第2章 2-8　 / 令和6年度 / 令和7年度 / 令和8年度（行：福島県平均（59市町村））</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9999,9 +10031,9 @@
           <t>第2章 2-8　 / 令和6年度 / 令和7年度 / 令和8年度（行：全国平均）</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>表と図が同じ数値を持ちます。数値を直すときは両方を直してください</t>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>

--- a/output/11_北塩原村第10期_図表データ管理台帳.xlsx
+++ b/output/11_北塩原村第10期_図表データ管理台帳.xlsx
@@ -12,27 +12,28 @@
     <sheet name="02_素案の表との突合" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="03_交付金との紐付け" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="04_資8の一覧との突合" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="D_fig2-1_人口構成比較" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="D_fig2-2_高齢化率推移" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="D_fig2-3_将来推計人口" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="D_fig2-4_前期後期高齢者" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="D_fig2-5_認定率推移" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="D_fig2-6_要介護度別認定者数" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="D_fig2-7_要支援1" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="D_fig2-8_新規認定要支援1" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="D_fig2-9_1人あたり費用額" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="D_fig2-10_費用額内訳" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="D_fig2-11_在宅施設別給付月額" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="D_fig2-14_サービス区分別変化" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="D_fig2-12_1人あたり定員" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="D_fig2-13_地域支援事業費" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="D_fig2-20_通いの場" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="D_fig2-15_財政指数" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="D_fig2-16_保険料比較" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="D_fig2-17_保険料と必要額" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="D_fig2-18_交付金指標群" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="D_fig2-19_交付金得点推移" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="99_自己点検" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="D_fig2-21_調整済み認定率" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="D_fig2-1_人口構成比較" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="D_fig2-2_高齢化率推移" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="D_fig2-3_将来推計人口" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="D_fig2-4_前期後期高齢者" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="D_fig2-5_認定率推移" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="D_fig2-6_要介護度別認定者数" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="D_fig2-7_要支援1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="D_fig2-8_新規認定要支援1" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="D_fig2-9_1人あたり費用額" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="D_fig2-10_費用額内訳" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="D_fig2-11_在宅施設別給付月額" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="D_fig2-14_サービス区分別変化" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="D_fig2-12_1人あたり定員" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="D_fig2-13_地域支援事業費" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="D_fig2-20_通いの場" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="D_fig2-15_財政指数" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="D_fig2-16_保険料比較" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="D_fig2-17_保険料と必要額" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="D_fig2-18_交付金指標群" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="D_fig2-19_交付金得点推移" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="99_自己点検" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -291,22 +292,21 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>年齢階級別人口の比較（平成22年・令和7年）</a:t>
+              <a:t>性・年齢調整済み認定率の推移（要介護度の区分別）</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
+      <lineChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'D_fig2-1_人口構成比較'!B5</f>
+              <f>'D_fig2-21_調整済み認定率'!B5</f>
             </strRef>
           </tx>
           <spPr>
@@ -314,14 +314,22 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
           <cat>
             <numRef>
-              <f>'D_fig2-1_人口構成比較'!$A$6:$A$10</f>
+              <f>'D_fig2-21_調整済み認定率'!$A$6:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'D_fig2-1_人口構成比較'!$B$6:$B$10</f>
+              <f>'D_fig2-21_調整済み認定率'!$B$6:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -330,7 +338,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'D_fig2-1_人口構成比較'!C5</f>
+              <f>'D_fig2-21_調整済み認定率'!C5</f>
             </strRef>
           </tx>
           <spPr>
@@ -338,21 +346,92 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
           <cat>
             <numRef>
-              <f>'D_fig2-1_人口構成比較'!$A$6:$A$10</f>
+              <f>'D_fig2-21_調整済み認定率'!$A$6:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'D_fig2-1_人口構成比較'!$C$6:$C$10</f>
+              <f>'D_fig2-21_調整済み認定率'!$C$6:$C$12</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-21_調整済み認定率'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'D_fig2-21_調整済み認定率'!$A$6:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-21_調整済み認定率'!$D$6:$D$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-21_調整済み認定率'!E5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'D_fig2-21_調整済み認定率'!$A$6:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-21_調整済み認定率'!$E$6:$E$12</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
-      </barChart>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -386,6 +465,159 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-9_1人あたり費用額'!B5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-9_1人あたり費用額'!$B$6:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-9_1人あたり費用額'!C5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-9_1人あたり費用額'!$C$6:$C$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-9_1人あたり費用額'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-9_1人あたり費用額'!$D$6:$D$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -517,7 +749,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -638,7 +870,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -745,7 +977,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -866,7 +1098,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1022,7 +1254,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1105,7 +1337,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1258,7 +1490,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1389,7 +1621,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1510,7 +1742,114 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>年齢階級別人口の比較（平成22年・令和7年）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-1_人口構成比較'!B5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_fig2-1_人口構成比較'!$A$6:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-1_人口構成比較'!$B$6:$B$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-1_人口構成比較'!C5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'D_fig2-1_人口構成比較'!$A$6:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-1_人口構成比較'!$C$6:$C$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1617,160 +1956,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>高齢化率の推移と将来推計（村・福島県・全国）</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'D_fig2-2_高齢化率推移'!B5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'D_fig2-2_高齢化率推移'!$A$6:$A$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'D_fig2-2_高齢化率推移'!$B$6:$B$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'D_fig2-2_高齢化率推移'!C5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'D_fig2-2_高齢化率推移'!$A$6:$A$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'D_fig2-2_高齢化率推移'!$C$6:$C$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'D_fig2-2_高齢化率推移'!D5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'D_fig2-2_高齢化率推移'!$A$6:$A$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'D_fig2-2_高齢化率推移'!$D$6:$D$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1936,6 +2122,159 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>高齢化率の推移と将来推計（村・福島県・全国）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-2_高齢化率推移'!B5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'D_fig2-2_高齢化率推移'!$A$6:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-2_高齢化率推移'!$B$6:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-2_高齢化率推移'!C5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'D_fig2-2_高齢化率推移'!$A$6:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-2_高齢化率推移'!$C$6:$C$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'D_fig2-2_高齢化率推移'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'D_fig2-2_高齢化率推移'!$A$6:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'D_fig2-2_高齢化率推移'!$D$6:$D$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>将来推計人口（年齢3区分）</a:t>
             </a:r>
           </a:p>
@@ -2079,7 +2418,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -2187,7 +2526,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -2340,7 +2679,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -2568,7 +2907,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -2651,7 +2990,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -2734,164 +3073,11 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'D_fig2-9_1人あたり費用額'!B5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$B$6:$B$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'D_fig2-9_1人あたり費用額'!C5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$C$6:$C$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'D_fig2-9_1人あたり費用額'!D5</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$D$6:$D$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -2945,7 +3131,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3026,7 +3212,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3053,7 +3239,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3080,7 +3266,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3134,7 +3320,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3188,7 +3374,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3212,6 +3398,33 @@
 </file>
 
 <file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -3242,7 +3455,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3269,7 +3482,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3296,7 +3509,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3323,7 +3536,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3350,7 +3563,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3404,7 +3617,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -3892,26 +4105,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-5　要支援・要介護認定率の推移（村・福島県・全国）</t>
+          <t>図2-4　前期高齢者と後期高齢者の推移</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：折れ線／掲載箇所：第2章 2-3／単位：%　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：積上げ棒／掲載箇所：第2章 2-2／単位：人　　出典：国立社会保障・人口問題研究所「日本の地域別将来推計人口」</t>
         </is>
       </c>
     </row>
@@ -3931,130 +4143,130 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>65〜74歳</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>福島県</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>全国</t>
+          <t>75歳以上</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>令和2年3月末</t>
+          <t>2010年</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>17.4</v>
+        <v>345</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>18.4</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>令和3年3月末</t>
+          <t>2015年</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>18.2</v>
+        <v>399</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>18.7</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>令和4年3月末</t>
+          <t>2020年</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>18.4</v>
+        <v>507</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>18.9</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>令和5年3月末</t>
+          <t>2025年</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>18.8</v>
+        <v>457</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>19</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>令和6年3月末</t>
+          <t>2030年</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>19.9</v>
+        <v>360</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>19.4</v>
+        <v>551</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>令和7年3月末</t>
+          <t>2035年</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>19.6</v>
+        <v>302</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>19.7</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>令和8年3月末</t>
+          <t>2040年</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>21.1</v>
+        <v>246</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>20.2</v>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>2045年</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>235</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>2050年</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>221</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -4069,6 +4281,188 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>図2-5　要支援・要介護認定率の推移（村・福島県・全国）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>種類：折れ線／掲載箇所：第2章 2-3／単位：%　　出典：地域包括ケア「見える化」システム</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>令和2年3月末</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>令和3年3月末</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>令和4年3月末</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>令和5年3月末</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>令和6年3月末</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>令和7年3月末</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>令和8年3月末</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4358,7 +4752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4473,124 +4867,6 @@
       </c>
       <c r="B12" s="16" t="n">
         <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>図2-8　新規認定者に占める要支援1の割合</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>種類：棒／掲載箇所：第2章 2-3／単位：%　　出典：地域包括ケア「見える化」システム</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>要支援1の割合</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>令和元年度</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>24.1</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>令和2年度</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>21.7</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>令和3年度</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>28.6</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>令和4年度</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>35.3</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>令和5年度</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>41.5</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>令和6年度</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>40.6</v>
       </c>
     </row>
   </sheetData>
@@ -4610,26 +4886,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-9　第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
+          <t>図2-8　新規認定者に占める要支援1の割合</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：折れ線／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：棒／掲載箇所：第2章 2-3／単位：%　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
@@ -4649,162 +4923,68 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>北塩原村</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>福島県</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>全国</t>
+          <t>要支援1の割合</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>平成29年度</t>
+          <t>令和元年度</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>25039</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>24056</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>23238</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>平成30年度</t>
+          <t>令和2年度</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>25606</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>24449</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>23499</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>令和元年度</t>
+          <t>令和3年度</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>23624</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>24819</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>24106</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>令和2年度</t>
+          <t>令和4年度</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>22072</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>25213</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>24567</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>令和3年度</t>
+          <t>令和5年度</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>21041</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>25426</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>25137</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>令和4年度</t>
+          <t>令和6年度</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>21563</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>25477</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>25471</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>令和5年度</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>23008</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>25871</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>26229</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>令和6年度</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>22751</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>26518</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>27147</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>令和7年度</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>24696</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>26848</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>27815</v>
+        <v>40.6</v>
       </c>
     </row>
   </sheetData>
@@ -4836,14 +5016,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-10　サービス区分別 費用額の推移</t>
+          <t>図2-10　第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：積上げ棒／掲載箇所：第2章 2-4／単位：百万円　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：折れ線／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
@@ -4863,17 +5043,17 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>在宅サービス</t>
+          <t>北塩原村</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>居住系サービス</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>施設サービス</t>
+          <t>全国</t>
         </is>
       </c>
     </row>
@@ -4884,13 +5064,13 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>103.5</v>
+        <v>25039</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>61.4</v>
+        <v>24056</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>133.6</v>
+        <v>23238</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -4900,13 +5080,13 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>94.7</v>
+        <v>25606</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>63.1</v>
+        <v>24449</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>150.3</v>
+        <v>23499</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -4916,13 +5096,13 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>81.5</v>
+        <v>23624</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>69.90000000000001</v>
+        <v>24819</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>138</v>
+        <v>24106</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4932,13 +5112,13 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>85</v>
+        <v>22072</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>74</v>
+        <v>25213</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>124.2</v>
+        <v>24567</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -4948,13 +5128,13 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>87.3</v>
+        <v>21041</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>64.59999999999999</v>
+        <v>25426</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>118</v>
+        <v>25137</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -4964,13 +5144,13 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>74.40000000000001</v>
+        <v>21563</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>69.5</v>
+        <v>25477</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>130</v>
+        <v>25471</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -4980,13 +5160,13 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>75.5</v>
+        <v>23008</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>76.40000000000001</v>
+        <v>25871</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>134.8</v>
+        <v>26229</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -4996,13 +5176,13 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>84.5</v>
+        <v>22751</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>81.40000000000001</v>
+        <v>26518</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>120.8</v>
+        <v>27147</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -5012,13 +5192,13 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>95.40000000000001</v>
+        <v>24696</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>91</v>
+        <v>26848</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>120.2</v>
+        <v>27815</v>
       </c>
     </row>
   </sheetData>
@@ -5044,19 +5224,20 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-11　在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
+          <t>図2-11　サービス区分別 費用額の推移</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：折れ線／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：積上げ棒／掲載箇所：第2章 2-4／単位：百万円　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
@@ -5081,125 +5262,157 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス</t>
+          <t>居住系サービス</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>施設サービス</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>H29年度</t>
+          <t>平成29年度</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>8157</v>
+        <v>103.5</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>15127</v>
+        <v>61.4</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>133.6</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>H30年度</t>
+          <t>平成30年度</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>7334</v>
+        <v>94.7</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>16286</v>
+        <v>63.1</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>150.3</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>R元年度</t>
+          <t>令和元年度</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>6198</v>
+        <v>81.5</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>15561</v>
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>R2年度</t>
+          <t>令和2年度</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>6324</v>
+        <v>85</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>14531</v>
+        <v>74</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>124.2</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>R3年度</t>
+          <t>令和3年度</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>6527</v>
+        <v>87.3</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>13422</v>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>R4年度</t>
+          <t>令和4年度</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>5597</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>14729</v>
+        <v>69.5</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>R5年度</t>
+          <t>令和5年度</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>5737</v>
+        <v>75.5</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>15747</v>
+        <v>76.40000000000001</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>134.8</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>R6年度</t>
+          <t>令和6年度</t>
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>6329</v>
+        <v>84.5</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>14915</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>120.8</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>R7年度</t>
+          <t>令和7年度</t>
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>7154</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>15651</v>
+        <v>91</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>120.2</v>
       </c>
     </row>
   </sheetData>
@@ -5219,7 +5432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5230,14 +5443,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-12　サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
+          <t>図2-12　在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：横棒／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：折れ線／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
@@ -5257,104 +5470,130 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>平成29年度</t>
+          <t>在宅サービス</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和7年度</t>
+          <t>施設・居住系サービス</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>訪問系</t>
+          <t>H29年度</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>1481</v>
+        <v>8157</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>728</v>
+        <v>15127</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>通所系</t>
+          <t>H30年度</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>4166</v>
+        <v>7334</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>3851</v>
+        <v>16286</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>短期入所</t>
+          <t>R元年度</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>756</v>
+        <v>6198</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>593</v>
+        <v>15561</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>福祉用具・住宅改修</t>
+          <t>R2年度</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>628</v>
+        <v>6324</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>879</v>
+        <v>14531</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>居宅介護支援</t>
+          <t>R3年度</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>1127</v>
+        <v>6527</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>1103</v>
+        <v>13422</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>居住系</t>
+          <t>R4年度</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>4740</v>
+        <v>5597</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>6748</v>
+        <v>14729</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>施設系</t>
+          <t>R5年度</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>10387</v>
+        <v>5737</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>8903</v>
+        <v>15747</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>R6年度</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>6329</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>14915</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>R7年度</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>7154</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>15651</v>
       </c>
     </row>
   </sheetData>
@@ -5374,7 +5613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5385,14 +5624,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-14　要支援・要介護者1人あたり定員の推移（定員は平成30年度以降据置）</t>
+          <t>図2-13　サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：折れ線／掲載箇所：第2章 2-5／単位：人　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：横棒／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
@@ -5412,156 +5651,104 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>通所系（通所介護）</t>
+          <t>平成29年度</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>居住系（認知症GH）</t>
+          <t>令和7年度</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>H27年度</t>
+          <t>訪問系</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.204</v>
+        <v>1481</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>0.092</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>H28年度</t>
+          <t>通所系</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>0.223</v>
+        <v>4166</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>0.134</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>H29年度</t>
+          <t>短期入所</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>0.233</v>
+        <v>756</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>0.14</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>H30年度</t>
+          <t>福祉用具・住宅改修</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>0.273</v>
+        <v>628</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>0.148</v>
+        <v>879</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>R元年度</t>
+          <t>居宅介護支援</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>0.287</v>
+        <v>1127</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>0.155</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>R2年度</t>
+          <t>居住系</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>0.269</v>
+        <v>4740</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>0.145</v>
+        <v>6748</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>R3年度</t>
+          <t>施設系</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>0.267</v>
+        <v>10387</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>0.144</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>R4年度</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>0.141</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>R5年度</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>R6年度</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>0.136</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>R7年度</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>0.126</v>
+        <v>8903</v>
       </c>
     </row>
   </sheetData>
@@ -5581,27 +5768,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-16　地域支援事業費の推移（内訳別）</t>
+          <t>図2-15　要支援・要介護者1人あたり定員の推移（定員は平成30年度以降据置）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：積上げ棒／掲載箇所：第2章 2-6／単位：百万円　　出典：介護保険特別会計決算</t>
+          <t>種類：折れ線／掲載箇所：第2章 2-5／単位：人　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
@@ -5621,163 +5806,163 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>一般介護予防事業費</t>
+          <t>通所系（通所介護）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>介護予防・生活支援サービス事業費</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>包括的支援事業費</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>その他</t>
+          <t>居住系（認知症GH）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>平成29年度</t>
+          <t>H27年度</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>1.71</v>
+        <v>0.204</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>5.4</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>平成30年度</t>
+          <t>H28年度</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>1.61</v>
+        <v>0.223</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>9.92</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>令和元年度</t>
+          <t>H29年度</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>1.77</v>
+        <v>0.233</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>10.54</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>令和2年度</t>
+          <t>H30年度</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>1.34</v>
+        <v>0.273</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>11.73</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>令和3年度</t>
+          <t>R元年度</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>1.09</v>
+        <v>0.287</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>令和4年度</t>
+          <t>R2年度</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>1.78</v>
+        <v>0.269</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>23.79</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>令和5年度</t>
+          <t>R3年度</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>1.83</v>
+        <v>0.267</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>R4年度</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>R5年度</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>R6年度</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>0.136</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>R7年度</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>0.126</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5790,7 +5975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6187,12 +6372,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
+          <t>性・年齢調整済み認定率の推移（要介護度の区分別）</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-4</t>
+          <t>第2章 2-3</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -6201,10 +6386,10 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -6216,7 +6401,11 @@
           <t>地域包括ケア「見える化」システム</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>性・年齢調整済み認定率は、全国の人口構成に合わせて年齢構成の違いを取り除いた認定率。要介護2以上は国の評価指標の成果指標にあたる。</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -6226,7 +6415,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>サービス区分別 費用額の推移</t>
+          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -6236,7 +6425,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>積上げ棒</t>
+          <t>折れ線</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -6265,7 +6454,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
+          <t>サービス区分別 費用額の推移</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -6275,14 +6464,14 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>折れ線</t>
+          <t>積上げ棒</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -6304,7 +6493,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
+          <t>在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -6314,11 +6503,11 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>横棒</t>
+          <t>折れ線</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>2</v>
@@ -6343,7 +6532,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>受給率の内訳（在宅・居住系・施設別）</t>
+          <t>サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -6353,22 +6542,18 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>不可（算定）</t>
+          <t>横棒</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>可</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -6376,11 +6561,7 @@
           <t>地域包括ケア「見える化」システム</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>「見える化」システムの合計受給率（在宅・居住系・施設）から読む</t>
-        </is>
-      </c>
+      <c r="I18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -6390,28 +6571,32 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>要支援・要介護者1人あたり定員の推移（定員は平成30年度以降据置）</t>
+          <t>受給率の内訳（在宅・居住系・施設別）</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-5</t>
+          <t>第2章 2-4</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>折れ線</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>可</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>不可（算定）</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -6419,7 +6604,11 @@
           <t>地域包括ケア「見える化」システム</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>「見える化」システムの合計受給率（在宅・居住系・施設）から読む</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -6429,7 +6618,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>事業所数からみた供給体制の位置（偏差値）</t>
+          <t>要支援・要介護者1人あたり定員の推移（定員は平成30年度以降据置）</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -6439,22 +6628,18 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>不可（算定）</t>
+          <t>折れ線</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>可</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -6462,11 +6647,7 @@
           <t>地域包括ケア「見える化」システム</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>「見える化」システムのサービス提供体制（供給）の偏差値から読む</t>
-        </is>
-      </c>
+      <c r="I20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -6476,36 +6657,44 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>地域支援事業費の推移（内訳別）</t>
+          <t>事業所数からみた供給体制の位置（偏差値）</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-6</t>
+          <t>第2章 2-5</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>積上げ棒</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>可</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>不可（算定）</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>介護保険特別会計決算</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr"/>
+          <t>地域包括ケア「見える化」システム</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>「見える化」システムのサービス提供体制（供給）の偏差値から読む</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
@@ -6515,7 +6704,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>住民主体の通いの場の状況（令和6年度）</t>
+          <t>地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -6525,15 +6714,15 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>棒</t>
+          <t>積上げ棒</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
           <t>可</t>
@@ -6541,14 +6730,10 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>厚生労働省「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>参加率の分母は65歳以上人口1,009人。全体27.8%・週1回以上12.2%</t>
-        </is>
-      </c>
+          <t>介護保険特別会計決算</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -6558,24 +6743,24 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
+          <t>住民主体の通いの場の状況（令和6年度）</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-7</t>
+          <t>第2章 2-6</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>折れ線</t>
+          <t>棒</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -6584,12 +6769,12 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>介護保険特別会計決算</t>
+          <t>厚生労働省「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>図は平成26年度＝100とした指数で描く。本表は決算の実額</t>
+          <t>参加率の分母は65歳以上人口1,009人。全体27.8%・週1回以上12.2%</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6786,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>介護保険料基準額の推移（村・福島県・全国）</t>
+          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -6611,11 +6796,11 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>棒</t>
+          <t>折れ線</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>3</v>
@@ -6627,10 +6812,14 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システム</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr"/>
+          <t>介護保険特別会計決算</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>図は平成26年度＝100とした指数で描く。本表は決算の実額</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -6640,7 +6829,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
+          <t>介護保険料基準額の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -6650,14 +6839,14 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>折れ線</t>
+          <t>棒</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -6679,17 +6868,17 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
+          <t>保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-8</t>
+          <t>第2章 2-7</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>棒</t>
+          <t>折れ線</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -6705,7 +6894,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>厚生労働省「令和8年度評価指標に係る該当状況調査票集計表」</t>
+          <t>地域包括ケア「見える化」システム</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr"/>
@@ -6718,7 +6907,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -6728,14 +6917,14 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>折れ線</t>
+          <t>棒</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -6744,7 +6933,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>厚生労働省「評価指標に係る該当状況調査票集計表」（令和6〜8年度）</t>
+          <t>厚生労働省「令和8年度評価指標に係る該当状況調査票集計表」</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr"/>
@@ -6752,64 +6941,56 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>図3-1</t>
+          <t>図2-23</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>施策の体系</t>
+          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>第3章 3-4</t>
+          <t>第2章 2-8</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>不可（算定）</t>
+          <t>折れ線</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>可</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>施策の体系図（数値を持たない）</t>
-        </is>
-      </c>
+          <t>厚生労働省「評価指標に係る該当状況調査票集計表」（令和6〜8年度）</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>図5-1</t>
+          <t>図3-1</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>需要に対する供給（担い手の枠）</t>
+          <t>施策の体系</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>第5章 5-4</t>
+          <t>第3章 3-4</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -6834,57 +7015,104 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>総務省「国勢調査」、国立社会保障・人口問題研究所「日本の地域別将来推計人口」、地域包括ケア「見える化」システムにより算定</t>
+          <t>―</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>estimate_jinzai.py の算定による</t>
+          <t>施策の体系図（数値を持たない）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
+          <t>図5-1</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>需要に対する供給（担い手の枠）</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>第5章 5-4</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>不可（算定）</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>総務省「国勢調査」、国立社会保障・人口問題研究所「日本の地域別将来推計人口」、地域包括ケア「見える化」システムにより算定</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>estimate_jinzai.py の算定による</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t>図5-2</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>算定上の保険料月額と条例上の基準額</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>第5章 5-7</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>不可（算定）</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>本計画の算定による</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>data/第10期_保険料パターン.csv による</t>
         </is>
@@ -6905,24 +7133,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-17　住民主体の通いの場の状況（令和6年度）</t>
+          <t>図2-17　地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：棒／掲載箇所：第2章 2-6／単位：か所／人　　出典：厚生労働省「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」　　注：参加率の分母は65歳以上人口1,009人。全体27.8%・週1回以上12.2%</t>
+          <t>種類：積上げ棒／掲載箇所：第2章 2-6／単位：百万円　　出典：介護保険特別会計決算</t>
         </is>
       </c>
     </row>
@@ -6942,55 +7173,163 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>値</t>
+          <t>一般介護予防事業費</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・生活支援サービス事業費</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業費</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>その他</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>箇所数 全体</t>
+          <t>平成29年度</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>23</v>
+        <v>1.71</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>5.4</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>箇所数 週1回以上</t>
+          <t>平成30年度</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>8</v>
+        <v>1.61</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>9.92</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>参加者数 全体</t>
+          <t>令和元年度</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>281</v>
+        <v>1.77</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>10.54</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>参加者数 週1回以上</t>
+          <t>令和2年度</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>123</v>
+        <v>1.34</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>11.73</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>令和3年度</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>令和4年度</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>令和5年度</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7003,26 +7342,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-18　保険給付費・地域支援事業費・保険料収入の推移</t>
+          <t>図2-18　住民主体の通いの場の状況（令和6年度）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：折れ線／掲載箇所：第2章 2-7／単位：千円　　出典：介護保険特別会計決算　　注：図は平成26年度＝100とした指数で描く。本表は決算の実額</t>
+          <t>種類：棒／掲載箇所：第2章 2-6／単位：か所／人　　出典：厚生労働省「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」　　注：参加率の分母は65歳以上人口1,009人。全体27.8%・週1回以上12.2%</t>
         </is>
       </c>
     </row>
@@ -7042,178 +7379,48 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>保険給付費</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業費</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>保険料収入</t>
+          <t>値</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>H26年度</t>
+          <t>箇所数 全体</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>279774</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>15580</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>48998</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>H27年度</t>
+          <t>箇所数 週1回以上</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>284396</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>16246</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>55142</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>H28年度</t>
+          <t>参加者数 全体</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>281570</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>22780</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>55416</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>H29年度</t>
+          <t>参加者数 週1回以上</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>290913</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>28727</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>56268</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>H30年度</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>302371</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>33471</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>65179</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>R元年度</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>286563</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>35671</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>64863</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>R2年度</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>279049</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>37451</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>64824</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>R3年度</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>266191</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>35216</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>69796</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>R4年度</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>271863</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>39754</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>69558</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>R5年度</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>280366</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>39886</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>69539</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -7233,7 +7440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7245,14 +7452,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-19　介護保険料基準額の推移（村・福島県・全国）</t>
+          <t>図2-19　保険給付費・地域支援事業費・保険料収入の推移</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：棒／掲載箇所：第2章 2-7／単位：円／月　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：折れ線／掲載箇所：第2章 2-7／単位：千円　　出典：介護保険特別会計決算　　注：図は平成26年度＝100とした指数で描く。本表は決算の実額</t>
         </is>
       </c>
     </row>
@@ -7272,66 +7479,178 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>保険給付費</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>福島県平均</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>全国平均</t>
+          <t>保険料収入</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>第7期（H30〜R2）</t>
+          <t>H26年度</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>5900</v>
+        <v>279774</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>6061</v>
+        <v>15580</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>5784</v>
+        <v>48998</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>第8期（R3〜R5）</t>
+          <t>H27年度</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>6300</v>
+        <v>284396</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>6108</v>
+        <v>16246</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>6014</v>
+        <v>55142</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>第9期（R6〜R8）</t>
+          <t>H28年度</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>6700</v>
+        <v>281570</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>6340</v>
+        <v>22780</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>6225</v>
+        <v>55416</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>H29年度</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>290913</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>28727</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>56268</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>H30年度</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>302371</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>33471</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>65179</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>R元年度</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>286563</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>35671</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>64863</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>R2年度</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>279049</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>37451</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>64824</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>R3年度</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>266191</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>35216</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>69796</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>R4年度</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>271863</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>39754</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>69558</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>R5年度</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>280366</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>39886</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>69539</v>
       </c>
     </row>
   </sheetData>
@@ -7351,25 +7670,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-20　保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
+          <t>図2-20　介護保険料基準額の推移（村・福島県・全国）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：折れ線／掲載箇所：第2章 2-7／単位：円／月　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：棒／掲載箇所：第2章 2-7／単位：円／月　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
@@ -7389,117 +7709,66 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>保険料基準額</t>
+          <t>北塩原村</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>必要保険料額</t>
+          <t>福島県平均</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>全国平均</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>H30年度</t>
+          <t>第7期（H30〜R2）</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
         <v>5900</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>6012</v>
+        <v>6061</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>5784</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>R元年度</t>
+          <t>第8期（R3〜R5）</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>5900</v>
+        <v>6300</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>6011</v>
+        <v>6108</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>6014</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>R2年度</t>
+          <t>第9期（R6〜R8）</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>5900</v>
+        <v>6700</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>5830</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>R3年度</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>6300</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>5451</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>R4年度</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>6300</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>6007</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>R5年度</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>6300</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>6335</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>R6年度</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>6700</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>5991</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>R7年度</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>6700</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>6501</v>
+        <v>6340</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>6225</v>
       </c>
     </row>
   </sheetData>
@@ -7530,14 +7799,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-21　交付金 目標別得点と全国平均の対比（令和8年度）</t>
+          <t>図2-21　保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：棒／掲載箇所：第2章 2-8／単位：点　　出典：厚生労働省「令和8年度評価指標に係る該当状況調査票集計表」</t>
+          <t>種類：折れ線／掲載箇所：第2章 2-7／単位：円／月　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
@@ -7557,117 +7826,117 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>保険料基準額</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>全国平均</t>
+          <t>必要保険料額</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>推進目標Ⅰ</t>
+          <t>H30年度</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>76</v>
+        <v>5900</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>62.3</v>
+        <v>6012</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>推進目標Ⅱ</t>
+          <t>R元年度</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>62</v>
+        <v>5900</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>69.2</v>
+        <v>6011</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>推進目標Ⅲ</t>
+          <t>R2年度</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>46</v>
+        <v>5900</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>50.8</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>推進目標Ⅳ</t>
+          <t>R3年度</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>45</v>
+        <v>6300</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>47.8</v>
+        <v>5451</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>支援目標Ⅰ</t>
+          <t>R4年度</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>71</v>
+        <v>6300</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>57.8</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>支援目標Ⅱ</t>
+          <t>R5年度</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>32</v>
+        <v>6300</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>51.1</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>支援目標Ⅲ</t>
+          <t>R6年度</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>70</v>
+        <v>6700</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>68.3</v>
+        <v>5991</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>支援目標Ⅳ</t>
+          <t>R7年度</t>
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>45</v>
+        <v>6700</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>47.8</v>
+        <v>6501</v>
       </c>
     </row>
   </sheetData>
@@ -7687,26 +7956,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-22　交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+          <t>図2-22　交付金 目標別得点と全国平均の対比（令和8年度）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：折れ線／掲載箇所：第2章 2-8／単位：点　　出典：厚生労働省「評価指標に係る該当状況調査票集計表」（令和6〜8年度）</t>
+          <t>種類：棒／掲載箇所：第2章 2-8／単位：点　　出典：厚生労働省「令和8年度評価指標に係る該当状況調査票集計表」</t>
         </is>
       </c>
     </row>
@@ -7731,11 +7999,6 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>福島県平均</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
           <t>全国平均</t>
         </is>
       </c>
@@ -7743,49 +8006,105 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>令和6年度</t>
+          <t>推進目標Ⅰ</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>354.1</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>422.4</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>令和7年度</t>
+          <t>推進目標Ⅱ</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>339</v>
+        <v>62</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>385.3</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>435</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>令和8年度</t>
+          <t>推進目標Ⅲ</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>447</v>
+        <v>46</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>456.4</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>455.1</v>
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>推進目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>支援目標Ⅰ</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>支援目標Ⅱ</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>51.1</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>支援目標Ⅲ</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>支援目標Ⅳ</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>47.8</v>
       </c>
     </row>
   </sheetData>
@@ -7805,6 +8124,124 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>図2-23　交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>種類：折れ線／掲載箇所：第2章 2-8／単位：点　　出典：厚生労働省「評価指標に係る該当状況調査票集計表」（令和6〜8年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>福島県平均</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>全国平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>295</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>354.1</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>422.4</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>339</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>447</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>455.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7872,7 +8309,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>25件</t>
+          <t>26件</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -7947,7 +8384,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>20枚／20件</t>
+          <t>21枚／21件</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -7972,7 +8409,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>25件</t>
+          <t>26件</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -7997,7 +8434,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>20件を照合</t>
+          <t>21件を照合</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -8097,7 +8534,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -8147,7 +8584,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>21件</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -8172,7 +8609,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>53系列</t>
+          <t>57系列</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -8197,7 +8634,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>20枚</t>
+          <t>21枚</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -8222,7 +8659,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>正本を参照30系列／図の間の重なり2系列／じか書き0系列／図のみ21系列／食い違い0系列</t>
+          <t>正本を参照34系列／図の間の重なり2系列／じか書き0系列／図のみ21系列／食い違い0系列</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -8272,7 +8709,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>0系列（正本を参照しているもの30系列）</t>
+          <t>0系列（正本を参照しているもの34系列）</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -8297,7 +8734,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>30／30系列</t>
+          <t>34／34系列</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -8346,7 +8783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8408,85 +8845,85 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>図2-1</t>
+          <t>図2-9</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>年齢階級別人口の比較（平成22年・令和7年）</t>
+          <t>性・年齢調整済み認定率の推移（要介護度の区分別）</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>平成22年（2010年）</t>
+          <t>合計</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（行：平成22年）</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>図と図が同じ数値を持ちます（図2-3・図2-4の平成22年（2010年）と重なる）。素案の表は重なり先の図を参照しています</t>
+          <t>第2章 2-3　時点 / 合計 / 軽度（要支援1〜要介護2） / 要介護2以上 / 重度（要介（列：合計）</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>図2-1</t>
+          <t>図2-9</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>年齢階級別人口の比較（平成22年・令和7年）</t>
+          <t>性・年齢調整済み認定率の推移（要介護度の区分別）</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>令和7年（2025年）</t>
+          <t>軽度（要支援1〜要介護2）</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（行：令和7年）</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>図と図が同じ数値を持ちます（図2-3・図2-4の令和7年（2025年）と重なる）。素案の表は重なり先の図を参照しています</t>
+          <t>第2章 2-3　時点 / 合計 / 軽度（要支援1〜要介護2） / 要介護2以上 / 重度（要介（列：軽度（要支援1〜要介護2））</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>図2-2</t>
+          <t>図2-9</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>高齢化率の推移と将来推計（村・福島県・全国）</t>
+          <t>性・年齢調整済み認定率の推移（要介護度の区分別）</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>要介護2以上</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 北塩原村 / 福島県 / 全国 / 県との差（列：北塩原村）</t>
+          <t>第2章 2-3　時点 / 合計 / 軽度（要支援1〜要介護2） / 要介護2以上 / 重度（要介（列：要介護2以上）</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -8498,25 +8935,25 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>図2-2</t>
+          <t>図2-9</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>高齢化率の推移と将来推計（村・福島県・全国）</t>
+          <t>性・年齢調整済み認定率の推移（要介護度の区分別）</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>重度（要介護3以上）</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 北塩原村 / 福島県 / 全国 / 県との差（列：福島県）</t>
+          <t>第2章 2-3　時点 / 合計 / 軽度（要支援1〜要介護2） / 要介護2以上 / 重度（要介（列：重度（要介護3以上））</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -8528,85 +8965,85 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>図2-2</t>
+          <t>図2-1</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>高齢化率の推移と将来推計（村・福島県・全国）</t>
+          <t>年齢階級別人口の比較（平成22年・令和7年）</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>平成22年（2010年）</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 北塩原村 / 福島県 / 全国 / 県との差（列：全国）</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（行：平成22年）</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>図と図が同じ数値を持ちます（図2-3・図2-4の平成22年（2010年）と重なる）。素案の表は重なり先の図を参照しています</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>図2-3</t>
+          <t>図2-1</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>将来推計人口（年齢3区分）</t>
+          <t>年齢階級別人口の比較（平成22年・令和7年）</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>15歳未満</t>
+          <t>令和7年（2025年）</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：15歳未満）</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（行：令和7年）</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>図と図が同じ数値を持ちます（図2-3・図2-4の令和7年（2025年）と重なる）。素案の表は重なり先の図を参照しています</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>図2-3</t>
+          <t>図2-2</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>将来推計人口（年齢3区分）</t>
+          <t>高齢化率の推移と将来推計（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>15〜64歳</t>
+          <t>北塩原村</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：生産年齢人口）</t>
+          <t>第2章 2-1　年 / 北塩原村 / 福島県 / 全国 / 県との差（列：北塩原村）</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -8618,25 +9055,25 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>図2-3</t>
+          <t>図2-2</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>将来推計人口（年齢3区分）</t>
+          <t>高齢化率の推移と将来推計（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>65歳以上</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>第5章 5-11　 / 令和7年 / 令和12年 / 令和17年 / 令和22年（行：高齢者人口）</t>
+          <t>第2章 2-1　年 / 北塩原村 / 福島県 / 全国 / 県との差（列：福島県）</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -8648,25 +9085,25 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>図2-3</t>
+          <t>図2-2</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>将来推計人口（年齢3区分）</t>
+          <t>高齢化率の推移と将来推計（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>総人口</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：総人口）</t>
+          <t>第2章 2-1　年 / 北塩原村 / 福島県 / 全国 / 県との差（列：全国）</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -8678,17 +9115,17 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>図2-4</t>
+          <t>図2-3</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>前期高齢者と後期高齢者の推移</t>
+          <t>将来推計人口（年齢3区分）</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>65〜74歳</t>
+          <t>15歳未満</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
@@ -8696,7 +9133,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：65〜74歳）</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：15歳未満）</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -8708,17 +9145,17 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>図2-4</t>
+          <t>図2-3</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>前期高齢者と後期高齢者の推移</t>
+          <t>将来推計人口（年齢3区分）</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>75歳以上</t>
+          <t>15〜64歳</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -8726,7 +9163,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：75歳以上）</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：生産年齢人口）</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -8738,17 +9175,17 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>図2-5</t>
+          <t>図2-3</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>要支援・要介護認定率の推移（村・福島県・全国）</t>
+          <t>将来推計人口（年齢3区分）</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>65歳以上</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
@@ -8756,7 +9193,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 北塩原村 / 福島県 / 全国（列：北塩原村）</t>
+          <t>第5章 5-11　 / 令和7年 / 令和12年 / 令和17年 / 令和22年（行：高齢者人口）</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -8768,17 +9205,17 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>図2-5</t>
+          <t>図2-3</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>要支援・要介護認定率の推移（村・福島県・全国）</t>
+          <t>将来推計人口（年齢3区分）</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>総人口</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
@@ -8786,7 +9223,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 北塩原村 / 福島県 / 全国（列：福島県）</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：総人口）</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -8798,17 +9235,17 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>図2-5</t>
+          <t>図2-4</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>要支援・要介護認定率の推移（村・福島県・全国）</t>
+          <t>前期高齢者と後期高齢者の推移</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>65〜74歳</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
@@ -8816,7 +9253,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 北塩原村 / 福島県 / 全国（列：全国）</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：65〜74歳）</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -8828,17 +9265,17 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>図2-6</t>
+          <t>図2-4</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>要介護度別 認定者数の推移</t>
+          <t>前期高齢者と後期高齢者の推移</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>要支援1</t>
+          <t>75歳以上</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
@@ -8846,7 +9283,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要支援1）</t>
+          <t>第2章 2-1　年 / 総人口 / 15歳未満 / 生産年齢人口 / 65〜74歳 / 75歳以（列：75歳以上）</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -8858,17 +9295,17 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>図2-6</t>
+          <t>図2-5</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>要介護度別 認定者数の推移</t>
+          <t>要支援・要介護認定率の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>要支援2</t>
+          <t>北塩原村</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
@@ -8876,7 +9313,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要支援2）</t>
+          <t>第2章 2-3　時点 / 北塩原村 / 福島県 / 全国（列：北塩原村）</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -8888,17 +9325,17 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>図2-6</t>
+          <t>図2-5</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>要介護度別 認定者数の推移</t>
+          <t>要支援・要介護認定率の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>要介護1</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
@@ -8906,7 +9343,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護1）</t>
+          <t>第2章 2-3　時点 / 北塩原村 / 福島県 / 全国（列：福島県）</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -8918,17 +9355,17 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>図2-6</t>
+          <t>図2-5</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>要介護度別 認定者数の推移</t>
+          <t>要支援・要介護認定率の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>要介護2</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
@@ -8936,7 +9373,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護2）</t>
+          <t>第2章 2-3　時点 / 北塩原村 / 福島県 / 全国（列：全国）</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -8958,7 +9395,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>要介護3</t>
+          <t>要支援1</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
@@ -8966,7 +9403,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護3）</t>
+          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要支援1）</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -8988,7 +9425,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>要介護4</t>
+          <t>要支援2</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
@@ -8996,7 +9433,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護4）</t>
+          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要支援2）</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -9018,7 +9455,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>要介護5</t>
+          <t>要介護1</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
@@ -9026,7 +9463,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護5）</t>
+          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護1）</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -9038,89 +9475,85 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>図2-7</t>
+          <t>図2-6</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>要支援1の認定者数の推移</t>
+          <t>要介護度別 認定者数の推移</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>要支援1</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護2）</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>図2-8</t>
+          <t>図2-6</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>新規認定者に占める要支援1の割合</t>
+          <t>要介護度別 認定者数の推移</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>要支援1の割合</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護3）</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>図2-9</t>
+          <t>図2-6</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
+          <t>要介護度別 認定者数の推移</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>要介護4</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-4　年度 / 北塩原村 / 福島県 / 全国 / 県との差（列：北塩原村）</t>
+          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護4）</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -9132,25 +9565,25 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>図2-9</t>
+          <t>図2-6</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
+          <t>要介護度別 認定者数の推移</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>要介護5</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-4　年度 / 北塩原村 / 福島県 / 全国 / 県との差（列：福島県）</t>
+          <t>第2章 2-3　時点 / 要支援1 / 要支援2 / 要介護1 / 要介護2 / 要介護3 / （列：要介護5）</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -9162,47 +9595,49 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>図2-9</t>
+          <t>図2-7</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
+          <t>要支援1の認定者数の推移</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>6</v>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-4　年度 / 北塩原村 / 福島県 / 全国 / 県との差（列：全国）</t>
+          <t>対応する表なし</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>図2-10</t>
+          <t>図2-8</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>サービス区分別 費用額の推移</t>
+          <t>新規認定者に占める要支援1の割合</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>在宅サービス</t>
+          <t>要支援1の割合</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -9229,27 +9664,25 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>サービス区分別 費用額の推移</t>
+          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>居住系サービス</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-4　年度 / 北塩原村 / 福島県 / 全国 / 県との差（列：北塩原村）</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9261,59 +9694,55 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>サービス区分別 費用額の推移</t>
+          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>施設サービス</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-4　年度 / 北塩原村 / 福島県 / 全国 / 県との差（列：福島県）</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>図2-11</t>
+          <t>図2-10</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
+          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>在宅サービス</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-4　年度 / 北塩原村 / 福島県 / 全国 / 県との差（列：全国）</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9325,12 +9754,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
+          <t>サービス区分別 費用額の推移</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>施設・居住系サービス</t>
+          <t>在宅サービス</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -9352,248 +9781,248 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>図2-12</t>
+          <t>図2-11</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
+          <t>サービス区分別 費用額の推移</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>平成29年度</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>7</v>
+          <t>居住系サービス</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-4　区分 / 平成29年度 / 令和7年度 / 増減 / 増減率 / 令和7年度の構（列：平成29年度）</t>
+          <t>対応する表なし</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>図2-12</t>
+          <t>図2-11</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
+          <t>サービス区分別 費用額の推移</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>令和7年度</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>7</v>
+          <t>施設サービス</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-4　区分 / 平成29年度 / 令和7年度 / 増減 / 増減率 / 令和7年度の構（列：令和7年度）</t>
+          <t>対応する表なし</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>図2-14</t>
+          <t>図2-12</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>要支援・要介護者1人あたり定員の推移（定員は平成30年度以降据置）</t>
+          <t>在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>通所系（通所介護）</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>5</v>
+          <t>在宅サービス</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-5　年度 / 居住系定員（認知症GH） / 通所系定員（通所介護） / 1人あたり定（列：1人あたり定員（通所系））</t>
+          <t>対応する表なし</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>図2-14</t>
+          <t>図2-12</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>要支援・要介護者1人あたり定員の推移（定員は平成30年度以降据置）</t>
+          <t>在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>居住系（認知症GH）</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>5</v>
+          <t>施設・居住系サービス</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-5　年度 / 居住系定員（認知症GH） / 通所系定員（通所介護） / 1人あたり定（列：1人あたり定員（居住系））</t>
+          <t>対応する表なし</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>図2-16</t>
+          <t>図2-13</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>地域支援事業費の推移（内訳別）</t>
+          <t>サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>一般介護予防事業費</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>平成29年度</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-4　区分 / 平成29年度 / 令和7年度 / 増減 / 増減率 / 令和7年度の構（列：平成29年度）</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>図2-16</t>
+          <t>図2-13</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>地域支援事業費の推移（内訳別）</t>
+          <t>サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>介護予防・生活支援サービス事業費</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-4　区分 / 平成29年度 / 令和7年度 / 増減 / 増減率 / 令和7年度の構（列：令和7年度）</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>図2-16</t>
+          <t>図2-15</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>地域支援事業費の推移（内訳別）</t>
+          <t>要支援・要介護者1人あたり定員の推移（定員は平成30年度以降据置）</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>包括的支援事業費</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>通所系（通所介護）</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-5　年度 / 居住系定員（認知症GH） / 通所系定員（通所介護） / 1人あたり定（列：1人あたり定員（通所系））</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>図2-16</t>
+          <t>図2-15</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>地域支援事業費の推移（内訳別）</t>
+          <t>要支援・要介護者1人あたり定員の推移（定員は平成30年度以降据置）</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>居住系（認知症GH）</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-5　年度 / 居住系定員（認知症GH） / 通所系定員（通所介護） / 1人あたり定（列：1人あたり定員（居住系））</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9605,12 +10034,12 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>住民主体の通いの場の状況（令和6年度）</t>
+          <t>地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>値</t>
+          <t>一般介護予防事業費</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -9632,47 +10061,49 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>図2-18</t>
+          <t>図2-17</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
+          <t>地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>保険給付費</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>3</v>
+          <t>介護予防・生活支援サービス事業費</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-9　年度 / 計画値 / 決算額 / 差（列：決算額）</t>
+          <t>対応する表なし</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>図2-18</t>
+          <t>図2-17</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
+          <t>地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>地域支援事業費</t>
+          <t>包括的支援事業費</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -9694,17 +10125,17 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>図2-18</t>
+          <t>図2-17</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
+          <t>地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>保険料収入</t>
+          <t>その他</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -9726,17 +10157,17 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>図2-19</t>
+          <t>図2-18</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>介護保険料基準額の推移（村・福島県・全国）</t>
+          <t>住民主体の通いの場の状況（令和6年度）</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>値</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -9763,27 +10194,25 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>介護保険料基準額の推移（村・福島県・全国）</t>
+          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>福島県平均</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>保険給付費</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>対応する表なし</t>
+          <t>第2章 2-9　年度 / 計画値 / 決算額 / 差（列：決算額）</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
       </c>
     </row>
@@ -9795,12 +10224,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>介護保険料基準額の推移（村・福島県・全国）</t>
+          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>全国平均</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -9822,17 +10251,17 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>図2-20</t>
+          <t>図2-19</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
+          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>保険料基準額</t>
+          <t>保険料収入</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -9859,12 +10288,12 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
+          <t>介護保険料基準額の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>必要保険料額</t>
+          <t>北塩原村</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -9886,17 +10315,17 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>図2-21</t>
+          <t>図2-20</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
+          <t>介護保険料基準額の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>福島県平均</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -9918,12 +10347,12 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>図2-21</t>
+          <t>図2-20</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
+          <t>介護保険料基準額の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -9950,60 +10379,64 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>図2-22</t>
+          <t>図2-21</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+          <t>保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>北塩原村</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>3</v>
+          <t>保険料基準額</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-8　 / 令和6年度 / 令和7年度 / 令和8年度（行：合計（800点））</t>
+          <t>対応する表なし</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>図2-22</t>
+          <t>図2-21</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+          <t>保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>福島県平均</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>3</v>
+          <t>必要保険料額</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-8　 / 令和6年度 / 令和7年度 / 令和8年度（行：福島県平均（59市町村））</t>
+          <t>対応する表なし</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
         </is>
       </c>
     </row>
@@ -10015,23 +10448,147 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
+          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>対応する表なし</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>図2-22</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>全国平均</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>対応する表なし</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>図だけが数値を持ちます。本表のデータシートで直せます</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>図2-23</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
           <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>第2章 2-8　 / 令和6年度 / 令和7年度 / 令和8年度（行：合計（800点））</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>図2-23</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>福島県平均</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>第2章 2-8　 / 令和6年度 / 令和7年度 / 令和8年度（行：福島県平均（59市町村））</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>図2-23</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>全国平均</t>
         </is>
       </c>
-      <c r="D58" s="7" t="n">
+      <c r="D62" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>第2章 2-8　 / 令和6年度 / 令和7年度 / 令和8年度（行：全国平均）</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>素案の表はこの系列を参照しています。本表のデータシートで直せば図と表の両方が変わります（片方だけが変わることはありません）</t>
         </is>
@@ -10164,7 +10721,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>図2-9／図2-10／図2-11／図2-12</t>
+          <t>図2-10／図2-11／図2-12／図2-13</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -10187,7 +10744,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>図2-13／図2-15</t>
+          <t>図2-14／図2-16</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -10210,7 +10767,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>図2-14／図2-15</t>
+          <t>図2-15／図2-16</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -10233,7 +10790,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>図2-16／図2-17</t>
+          <t>図2-17／図2-18</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -10256,7 +10813,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>図2-18／図2-19／図2-20</t>
+          <t>図2-19／図2-20／図2-21</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -10279,7 +10836,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>図2-21／図2-22</t>
+          <t>図2-22／図2-23</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -10338,54 +10895,54 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>在宅と施設の利用の分かれ方</t>
+          <t>自立支援・重度化防止の成果（認定率の変化）</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>推進Ⅰ</t>
+          <t>支援Ⅰ</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>図2-13</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>一部</t>
+          <t>図2-9</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>ある</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>在宅・居住系・施設の3区分で示しているが、要介護度別の内訳は表による</t>
+          <t>性・年齢調整済み認定率の推移を図にした。合計・軽度・要介護2以上・重度の4系列。国の成果指標（要介護2以上）の値と一致することを素案2-3の注記で示している</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>自立支援・重度化防止の成果（認定率の変化）</t>
+          <t>在宅と施設の利用の分かれ方</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>支援Ⅰ</t>
+          <t>推進Ⅰ</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>ない</t>
+          <t>図2-14</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>一部</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>性・年齢調整済み認定率の推移を図にしていない。値は素案2-8の表による</t>
+          <t>在宅・居住系・施設の3区分で示しているが、要介護度別の内訳は表による</t>
         </is>
       </c>
     </row>
@@ -10458,7 +11015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10703,12 +11260,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
+          <t>性・年齢調整済み認定率の推移（要介護度の区分別）</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-4</t>
+          <t>第2章 2-3</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -10726,7 +11283,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>サービス区分別 費用額の推移</t>
+          <t>第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -10749,7 +11306,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
+          <t>サービス区分別 費用額の推移</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -10772,7 +11329,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
+          <t>在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -10795,7 +11352,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>受給率の内訳（在宅・居住系・施設別）</t>
+          <t>サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -10818,12 +11375,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>要支援・要介護者1人あたり定員の推移</t>
+          <t>受給率の内訳（在宅・居住系・施設別）</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-5</t>
+          <t>第2章 2-4</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -10841,7 +11398,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>事業所数からみた供給体制の位置（偏差値）</t>
+          <t>要支援・要介護者1人あたり定員の推移</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -10864,12 +11421,12 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>地域支援事業費の推移（内訳別）</t>
+          <t>事業所数からみた供給体制の位置（偏差値）</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-6</t>
+          <t>第2章 2-5</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -10887,7 +11444,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>住民主体の通いの場の状況（令和6年度）</t>
+          <t>地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -10910,12 +11467,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
+          <t>住民主体の通いの場の状況（令和6年度）</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-7</t>
+          <t>第2章 2-6</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -10933,7 +11490,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>介護保険料基準額の推移（村・福島県・全国）</t>
+          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -10956,7 +11513,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>保険料基準額と必要保険料額の対比</t>
+          <t>介護保険料基準額の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -10979,12 +11536,12 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
+          <t>保険料基準額と必要保険料額の対比</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-8</t>
+          <t>第2章 2-7</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -11002,7 +11559,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -11020,17 +11577,17 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>図3-1</t>
+          <t>図2-23</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>施策の体系</t>
+          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>第3章 3-4</t>
+          <t>第2章 2-8</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -11043,17 +11600,17 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>図5-1</t>
+          <t>図3-1</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>需要に対する供給（担い手の枠）</t>
+          <t>施策の体系</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>第5章 5-4</t>
+          <t>第3章 3-4</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -11066,25 +11623,48 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
+          <t>図5-1</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>需要に対する供給（担い手の枠）</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>第5章 5-4</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t>図5-2</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>算定上の保険料月額と条例上の基準額</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>第5章 5-7</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11101,25 +11681,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-1　年齢階級別人口の比較（平成22年・令和7年）</t>
+          <t>図2-9　性・年齢調整済み認定率の推移（要介護度の区分別）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：横棒／掲載箇所：第2章 2-1／単位：人　　出典：総務省「国勢調査」、国立社会保障・人口問題研究所「日本の地域別将来推計人口」</t>
+          <t>種類：折れ線／掲載箇所：第2章 2-3／単位：%　　出典：地域包括ケア「見える化」システム（B5-a・B6-a・B6-b／注目する地域のみ）　　注：性・年齢調整済み認定率は、全国の人口構成に合わせて年齢構成の違いを取り除いた認定率。要介護2以上は国の評価指標の成果指標にあたる。</t>
         </is>
       </c>
     </row>
@@ -11139,85 +11721,163 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>平成22年（2010年）</t>
+          <t>合計</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和7年（2025年）</t>
+          <t>軽度（要支援1〜要介護2）</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>要介護2以上</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>重度（要介護3以上）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>15歳未満</t>
+          <t>令和2年3月末</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>415</v>
+        <v>19.5</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>186</v>
+        <v>12.8</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>15〜39歳</t>
+          <t>令和3年3月末</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>713</v>
+        <v>20.3</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>451</v>
+        <v>13.5</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>6.8</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>40〜64歳</t>
+          <t>令和4年3月末</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>1166</v>
+        <v>20.7</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>741</v>
+        <v>14.3</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>6.4</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>65〜74歳</t>
+          <t>令和5年3月末</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>345</v>
+        <v>21.3</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>457</v>
+        <v>14.7</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>75歳以上</t>
+          <t>令和6年3月末</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>546</v>
+        <v>22.1</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>480</v>
+        <v>16.4</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>令和7年3月末</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>令和8年3月末</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -11230,26 +11890,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>図2-2　高齢化率の推移と将来推計（村・福島県・全国）</t>
+          <t>図2-1　年齢階級別人口の比較（平成22年・令和7年）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>種類：折れ線／掲載箇所：第2章 2-1／単位：%　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：横棒／掲載箇所：第2章 2-1／単位：人　　出典：総務省「国勢調査」、国立社会保障・人口問題研究所「日本の地域別将来推計人口」</t>
         </is>
       </c>
     </row>
@@ -11269,162 +11928,78 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>平成22年（2010年）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>福島県</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>全国</t>
+          <t>令和7年（2025年）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>2010年</t>
+          <t>15歳未満</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>28</v>
+        <v>415</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>22.8</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>2015年</t>
+          <t>15〜39歳</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>31.8</v>
+        <v>713</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>26.3</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>2020年</t>
+          <t>40〜64歳</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>37.1</v>
+        <v>1166</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>28</v>
+        <v>741</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>65〜74歳</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>40.5</v>
+        <v>345</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>29.6</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>2030年</t>
+          <t>75歳以上</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>43.9</v>
+        <v>546</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>30.8</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>2035年</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>32.3</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>2040年</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>34.8</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>2045年</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>36.3</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>2050年</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>37.1</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -11444,6 +12019,220 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>図2-2　高齢化率の推移と将来推計（村・福島県・全国）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>種類：折れ線／掲載箇所：第2章 2-1／単位：%　　出典：地域包括ケア「見える化」システム</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>2010年</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>2015年</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>2020年</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>2030年</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>2035年</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>2040年</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>34.8</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>2045年</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>2050年</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11683,185 +12472,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>図2-4　前期高齢者と後期高齢者の推移</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>種類：積上げ棒／掲載箇所：第2章 2-2／単位：人　　出典：国立社会保障・人口問題研究所「日本の地域別将来推計人口」</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>65〜74歳</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>75歳以上</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>2010年</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>345</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>2015年</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>399</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>2020年</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>507</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>2025年</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>457</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>2030年</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>360</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>2035年</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>302</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>2040年</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>246</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>2045年</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>235</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>2050年</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>221</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>398</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/output/11_北塩原村第10期_図表データ管理台帳.xlsx
+++ b/output/11_北塩原村第10期_図表データ管理台帳.xlsx
@@ -94,7 +94,7 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -124,11 +124,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DEEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -163,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -189,9 +184,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -200,7 +192,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -4114,21 +4106,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-4　前期高齢者と後期高齢者の推移</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：積上げ棒／掲載箇所：第2章 2-2／単位：人　　出典：国立社会保障・人口問題研究所「日本の地域別将来推計人口」</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -4153,119 +4145,119 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>2010年</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>345</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>546</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>2015年</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>399</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>2020年</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>507</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>441</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>2025年</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>457</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>2030年</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>360</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>551</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>2035年</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>302</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>541</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>2040年</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>246</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>519</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>2045年</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>235</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>457</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>2050年</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>221</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>398</v>
       </c>
     </row>
@@ -4296,21 +4288,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-5　要支援・要介護認定率の推移（村・福島県・全国）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：折れ線／掲載箇所：第2章 2-3／単位：%　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -4340,114 +4332,114 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>令和2年3月末</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>17.4</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>19.2</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>18.4</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>令和3年3月末</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>18.2</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>19.3</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>18.7</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>令和4年3月末</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>18.4</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>19.3</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>18.9</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>令和5年3月末</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>18.8</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>19.2</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>令和6年3月末</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>19.9</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>19.3</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>19.4</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>令和7年3月末</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>19.6</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>19.5</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>19.7</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>令和8年3月末</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>21.1</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>19.8</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>20.2</v>
       </c>
     </row>
@@ -4482,21 +4474,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-6　要介護度別 認定者数の推移</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：積上げ棒／掲載箇所：第2章 2-3／単位：人　　出典：厚生労働省「介護保険事業状況報告」</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -4546,198 +4538,198 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>令和2年3月末</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>43</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="H6" s="15" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>令和3年3月末</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="15" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>令和4年3月末</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="15" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>令和5年3月末</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="15" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>令和6年3月末</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>51</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="15" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>令和7年3月末</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>47</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="15" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>令和8年3月末</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>51</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>49</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4766,21 +4758,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-7　要支援1の認定者数の推移</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：棒／掲載箇所：第2章 2-3／単位：人　　出典：厚生労働省「介護保険事業状況報告」</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -4800,72 +4792,72 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>令和2年</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>令和3年</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>令和4年</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>令和5年</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>令和6年</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>令和7年</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>令和8年</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>51</v>
       </c>
     </row>
@@ -4894,21 +4886,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-8　新規認定者に占める要支援1の割合</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：棒／掲載箇所：第2章 2-3／単位：%　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -4928,62 +4920,62 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>令和元年度</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>24.1</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>令和2年度</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>21.7</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>令和3年度</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>28.6</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>令和4年度</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>35.3</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>令和5年度</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>41.5</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>令和6年度</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>40.6</v>
       </c>
     </row>
@@ -5014,21 +5006,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-10　第1号被保険者1人1月あたり費用額（村・福島県・全国）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：折れ線／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -5058,146 +5050,146 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>平成29年度</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>25039</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>24056</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>23238</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>平成30年度</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>25606</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>24449</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>23499</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>令和元年度</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>23624</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>24819</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>24106</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>令和2年度</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>22072</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>25213</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>24567</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>令和3年度</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>21041</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>25426</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>25137</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>令和4年度</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>21563</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>25477</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>25471</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>令和5年度</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>23008</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>25871</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>26229</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>令和6年度</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>22751</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>26518</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <v>27147</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>24696</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>26848</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="15" t="n">
         <v>27815</v>
       </c>
     </row>
@@ -5228,21 +5220,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-11　サービス区分別 費用額の推移</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：積上げ棒／掲載箇所：第2章 2-4／単位：百万円　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -5272,146 +5264,146 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>平成29年度</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>103.5</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>61.4</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>133.6</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>平成30年度</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>94.7</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>63.1</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>150.3</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>令和元年度</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>81.5</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>138</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>令和2年度</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>85</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>74</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>124.2</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>令和3年度</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>87.3</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>118</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>令和4年度</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>69.5</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>令和5年度</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>75.5</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>134.8</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>令和6年度</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>84.5</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <v>120.8</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>91</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="15" t="n">
         <v>120.2</v>
       </c>
     </row>
@@ -5441,21 +5433,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-12　在宅・施設居住系別 第1号被保険者1人1月あたり給付月額</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：折れ線／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -5480,119 +5472,119 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H29年度</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>8157</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>15127</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H30年度</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>7334</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>16286</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>R元年度</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>6198</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>15561</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>R2年度</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>6324</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>14531</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>R3年度</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>6527</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>13422</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>R4年度</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>5597</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>14729</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>R5年度</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>5737</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>15747</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>R6年度</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>6329</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>14915</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>R7年度</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>7154</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>15651</v>
       </c>
     </row>
@@ -5622,21 +5614,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-13　サービス区分別 1人1月あたり給付月額の変化（平成29年度→令和7年度）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：横棒／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -5661,93 +5653,93 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>訪問系</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>1481</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>728</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>通所系</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>4166</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>3851</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>短期入所</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>756</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>593</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>福祉用具・住宅改修</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>628</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>879</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>居宅介護支援</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>1127</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>1103</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>居住系</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>4740</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>6748</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>施設系</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>10387</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>8903</v>
       </c>
     </row>
@@ -5777,21 +5769,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-15　要支援・要介護者1人あたり定員の推移（定員は平成30年度以降据置）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：折れ線／掲載箇所：第2章 2-5／単位：人　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -5816,145 +5808,145 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H27年度</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>0.204</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>0.092</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H28年度</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>0.223</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>0.134</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H29年度</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>0.233</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>0.14</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H30年度</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>0.273</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>0.148</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>R元年度</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>0.287</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>0.155</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>R2年度</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>0.269</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>0.145</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>R3年度</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>0.267</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>0.144</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>R4年度</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>0.262</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>0.141</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>R5年度</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>0.135</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>R6年度</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="15" t="n">
         <v>0.253</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="15" t="n">
         <v>0.136</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>R7年度</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="15" t="n">
         <v>0.234</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="15" t="n">
         <v>0.126</v>
       </c>
     </row>
@@ -5975,7 +5967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6704,33 +6696,37 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>地域支援事業費の推移（内訳別）</t>
+          <t>医療と介護の連携に関する加算の算定率と全国の中での位置</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-6</t>
+          <t>第2章 2-5</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>積上げ棒</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>可</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>不可（算定）</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>介護保険特別会計決算</t>
+          <t>地域包括ケア「見える化」システム　地域分析（医療介護連携）</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr"/>
@@ -6743,7 +6739,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>住民主体の通いの場の状況（令和6年度）</t>
+          <t>地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -6753,15 +6749,15 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>棒</t>
+          <t>積上げ棒</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
           <t>可</t>
@@ -6769,14 +6765,10 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>厚生労働省「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>参加率の分母は65歳以上人口1,009人。全体27.8%・週1回以上12.2%</t>
-        </is>
-      </c>
+          <t>介護保険特別会計決算</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
@@ -6786,24 +6778,24 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
+          <t>住民主体の通いの場の状況（令和6年度）</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-7</t>
+          <t>第2章 2-6</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>折れ線</t>
+          <t>棒</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -6812,12 +6804,12 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>介護保険特別会計決算</t>
+          <t>厚生労働省「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>図は平成26年度＝100とした指数で描く。本表は決算の実額</t>
+          <t>参加率の分母は65歳以上人口1,009人。全体27.8%・週1回以上12.2%</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6821,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>介護保険料基準額の推移（村・福島県・全国）</t>
+          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -6839,11 +6831,11 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>棒</t>
+          <t>折れ線</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>3</v>
@@ -6855,10 +6847,14 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システム</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr"/>
+          <t>介護保険特別会計決算</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>図は平成26年度＝100とした指数で描く。本表は決算の実額</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -6868,7 +6864,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
+          <t>介護保険料基準額の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -6878,14 +6874,14 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>折れ線</t>
+          <t>棒</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -6907,17 +6903,17 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
+          <t>保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-8</t>
+          <t>第2章 2-7</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>棒</t>
+          <t>折れ線</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
@@ -6933,7 +6929,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>厚生労働省「令和8年度評価指標に係る該当状況調査票集計表」</t>
+          <t>地域包括ケア「見える化」システム</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr"/>
@@ -6946,7 +6942,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -6956,14 +6952,14 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>折れ線</t>
+          <t>棒</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -6972,7 +6968,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>厚生労働省「評価指標に係る該当状況調査票集計表」（令和6〜8年度）</t>
+          <t>厚生労働省「令和8年度評価指標に係る該当状況調査票集計表」</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr"/>
@@ -6980,64 +6976,56 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>図3-1</t>
+          <t>図2-24</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>施策の体系</t>
+          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>第3章 3-4</t>
+          <t>第2章 2-8</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>不可（算定）</t>
+          <t>折れ線</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>可</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>施策の体系図（数値を持たない）</t>
-        </is>
-      </c>
+          <t>厚生労働省「評価指標に係る該当状況調査票集計表」（令和6〜8年度）</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>図5-1</t>
+          <t>図3-1</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>需要に対する供給（担い手の枠）</t>
+          <t>施策の体系</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>第5章 5-4</t>
+          <t>第3章 3-4</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -7062,61 +7050,151 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>総務省「国勢調査」、国立社会保障・人口問題研究所「日本の地域別将来推計人口」、地域包括ケア「見える化」システムにより算定</t>
+          <t>―</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>estimate_jinzai.py の算定による</t>
+          <t>施策の体系図（数値を持たない）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>図5-1</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>需要に対する供給（担い手の枠）</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>第5章 5-4</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>不可（算定）</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>総務省「国勢調査」、国立社会保障・人口問題研究所「日本の地域別将来推計人口」、地域包括ケア「見える化」システムにより算定</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>estimate_jinzai.py の算定による</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
           <t>図5-2</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>算定上の保険料月額と条例上の基準額</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>第5章 5-7</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>不可（算定）</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>本計画の算定による</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>data/第10期_保険料パターン.csv による</t>
         </is>
       </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>図5-3</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>給付適正化の取組別得点の推移（推進交付金 目標Ⅱ）</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>第5章 5-8</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>不可（算定）</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>厚生労働省「評価指標に係る該当状況調査票集計表」（令和6〜8年度）により算定</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7144,21 +7222,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>図2-17　地域支援事業費の推移（内訳別）</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図2-18　地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：積上げ棒／掲載箇所：第2章 2-6／単位：百万円　　出典：介護保険特別会計決算</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -7193,135 +7271,135 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>平成29年度</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>1.71</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>8.119999999999999</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>13.5</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>5.4</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>平成30年度</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>1.61</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>8.48</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>13.46</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="15" t="n">
         <v>9.92</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>令和元年度</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>1.77</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>9.48</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>13.89</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="15" t="n">
         <v>10.54</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>令和2年度</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>1.34</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>10.73</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>13.66</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="15" t="n">
         <v>11.73</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>令和3年度</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>1.09</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>10.8</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>23.33</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>令和4年度</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>1.78</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>14.18</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>23.79</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>令和5年度</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>1.83</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>14.64</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>23.42</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7350,21 +7428,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>図2-18　住民主体の通いの場の状況（令和6年度）</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図2-19　住民主体の通いの場の状況（令和6年度）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：棒／掲載箇所：第2章 2-6／単位：か所／人　　出典：厚生労働省「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」　　注：参加率の分母は65歳以上人口1,009人。全体27.8%・週1回以上12.2%</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -7384,42 +7462,42 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>箇所数 全体</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>箇所数 週1回以上</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>参加者数 全体</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>281</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>参加者数 週1回以上</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>123</v>
       </c>
     </row>
@@ -7450,21 +7528,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>図2-19　保険給付費・地域支援事業費・保険料収入の推移</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図2-20　保険給付費・地域支援事業費・保険料収入の推移</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：折れ線／掲載箇所：第2章 2-7／単位：千円　　出典：介護保険特別会計決算　　注：図は平成26年度＝100とした指数で描く。本表は決算の実額</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -7494,162 +7572,162 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H26年度</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>279774</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>15580</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>48998</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H27年度</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>284396</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>16246</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>55142</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H28年度</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>281570</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>22780</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>55416</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H29年度</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>290913</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>28727</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>56268</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>H30年度</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>302371</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>33471</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>65179</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>R元年度</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>286563</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>35671</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>64863</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>R2年度</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>279049</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>37451</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>64824</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>R3年度</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>266191</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>35216</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <v>69796</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>R4年度</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>271863</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>39754</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="15" t="n">
         <v>69558</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>R5年度</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="15" t="n">
         <v>280366</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="15" t="n">
         <v>39886</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="15" t="n">
         <v>69539</v>
       </c>
     </row>
@@ -7680,21 +7758,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>図2-20　介護保険料基準額の推移（村・福島県・全国）</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図2-21　介護保険料基準額の推移（村・福島県・全国）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：棒／掲載箇所：第2章 2-7／単位：円／月　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -7724,50 +7802,50 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>第7期（H30〜R2）</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>5900</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>6061</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>5784</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>第8期（R3〜R5）</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>6300</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>6108</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>6014</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>第9期（R6〜R8）</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>6700</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>6340</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>6225</v>
       </c>
     </row>
@@ -7797,21 +7875,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>図2-21　保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図2-22　保険料基準額と必要保険料額の対比（第8期以降は余剰が継続）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：折れ線／掲載箇所：第2章 2-7／単位：円／月　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -7836,106 +7914,106 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H30年度</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>5900</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>6012</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>R元年度</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>5900</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>6011</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>R2年度</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>5900</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>5830</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>R3年度</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>6300</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>5451</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>R4年度</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>6300</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>6007</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>R5年度</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>6300</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>6335</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>R6年度</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>6700</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>5991</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>R7年度</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>6700</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>6501</v>
       </c>
     </row>
@@ -7965,21 +8043,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>図2-22　交付金 目標別得点と全国平均の対比（令和8年度）</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図2-23　交付金 目標別得点と全国平均の対比（令和8年度）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：棒／掲載箇所：第2章 2-8／単位：点　　出典：厚生労働省「令和8年度評価指標に係る該当状況調査票集計表」</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -8004,106 +8082,106 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>推進目標Ⅰ</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>76</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>62.3</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>推進目標Ⅱ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>62</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>69.2</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>推進目標Ⅲ</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>50.8</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>推進目標Ⅳ</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>47.8</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>支援目標Ⅰ</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>71</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>57.8</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>支援目標Ⅱ</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>51.1</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>支援目標Ⅲ</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>68.3</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>支援目標Ⅳ</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>47.8</v>
       </c>
     </row>
@@ -8134,21 +8212,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>図2-23　交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>図2-24　交付金 合計得点の推移（村・福島県平均・全国平均）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：折れ線／掲載箇所：第2章 2-8／単位：点　　出典：厚生労働省「評価指標に係る該当状況調査票集計表」（令和6〜8年度）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -8178,50 +8256,50 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>令和6年度</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>295</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>354.1</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>422.4</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>339</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>385.3</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>435</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>447</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>456.4</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>455.1</v>
       </c>
     </row>
@@ -8309,7 +8387,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>26件</t>
+          <t>28件</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -8409,7 +8487,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>26件</t>
+          <t>28件</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -8534,7 +8612,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>0件</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -10029,7 +10107,7 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>図2-17</t>
+          <t>図2-18</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -10061,7 +10139,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>図2-17</t>
+          <t>図2-18</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -10093,7 +10171,7 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>図2-17</t>
+          <t>図2-18</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -10125,7 +10203,7 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>図2-17</t>
+          <t>図2-18</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -10157,7 +10235,7 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>図2-18</t>
+          <t>図2-19</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -10189,7 +10267,7 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>図2-19</t>
+          <t>図2-20</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -10219,7 +10297,7 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>図2-19</t>
+          <t>図2-20</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -10251,7 +10329,7 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>図2-19</t>
+          <t>図2-20</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -10283,7 +10361,7 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>図2-20</t>
+          <t>図2-21</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -10315,7 +10393,7 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>図2-20</t>
+          <t>図2-21</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -10347,7 +10425,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>図2-20</t>
+          <t>図2-21</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -10379,7 +10457,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>図2-21</t>
+          <t>図2-22</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -10411,7 +10489,7 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>図2-21</t>
+          <t>図2-22</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -10443,7 +10521,7 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>図2-22</t>
+          <t>図2-23</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -10475,7 +10553,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>図2-22</t>
+          <t>図2-23</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -10507,7 +10585,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>図2-23</t>
+          <t>図2-24</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -10537,7 +10615,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>図2-23</t>
+          <t>図2-24</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -10567,7 +10645,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>図2-23</t>
+          <t>図2-24</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -10790,7 +10868,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>図2-17／図2-18</t>
+          <t>図2-18／図2-19</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -10813,7 +10891,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>図2-19／図2-20／図2-21</t>
+          <t>図2-20／図2-21／図2-22</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -10836,7 +10914,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>図2-22／図2-23</t>
+          <t>図2-23／図2-24</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -10959,17 +11037,17 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>ない</t>
+          <t>図5-3</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>ある</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>ケアプラン点検の実績が村にないため図にできない（確認事項）</t>
+          <t>ケアプラン点検の実績そのものは村にないが、国の評価における取組別の得点（方策の策定・事業の取組・ケアプラン点検・医療情報との突合）を3か年で図にした。ケアプラン点検は令和8年度に4段階のうち2段階を取得している</t>
         </is>
       </c>
     </row>
@@ -10986,17 +11064,17 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>ない</t>
+          <t>図2-17</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>ある</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>加算の算定状況の集計が村にないため図にできない（確認事項・doc49 §2-4）</t>
+          <t>村の給付実績の集計を待たずに、「見える化」システムの地域分析（医療介護連携）に収録されている4加算の算定率と偏差値を図にした。緊急時訪問看護加算は村内に訪問看護事業所がないため値がない</t>
         </is>
       </c>
     </row>
@@ -11015,7 +11093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11444,12 +11522,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>地域支援事業費の推移（内訳別）</t>
+          <t>医療と介護の連携に関する加算の算定率と全国の中での位置</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-6</t>
+          <t>第2章 2-5</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -11467,7 +11545,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>住民主体の通いの場の状況（令和6年度）</t>
+          <t>地域支援事業費の推移（内訳別）</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -11490,12 +11568,12 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
+          <t>住民主体の通いの場の状況（令和6年度）</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-7</t>
+          <t>第2章 2-6</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -11513,7 +11591,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>介護保険料基準額の推移（村・福島県・全国）</t>
+          <t>保険給付費・地域支援事業費・保険料収入の推移</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -11536,7 +11614,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>保険料基準額と必要保険料額の対比</t>
+          <t>介護保険料基準額の推移（村・福島県・全国）</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -11559,12 +11637,12 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
+          <t>保険料基準額と必要保険料額の対比</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>第2章 2-8</t>
+          <t>第2章 2-7</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -11582,7 +11660,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
+          <t>交付金 目標別得点と全国平均の対比（令和8年度）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -11600,17 +11678,17 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>図3-1</t>
+          <t>図2-24</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>施策の体系</t>
+          <t>交付金 合計得点の推移（村・福島県平均・全国平均）</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>第3章 3-4</t>
+          <t>第2章 2-8</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -11623,17 +11701,17 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>図5-1</t>
+          <t>図3-1</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>需要に対する供給（担い手の枠）</t>
+          <t>施策の体系</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>第5章 5-4</t>
+          <t>第3章 3-4</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -11646,25 +11724,71 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>図5-1</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>需要に対する供給（担い手の枠）</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>第5章 5-4</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
           <t>図5-2</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>算定上の保険料月額と条例上の基準額</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>第5章 5-7</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>図5-3</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>給付適正化の取組別得点の推移（推進交付金 目標Ⅱ）</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>第5章 5-8</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11692,21 +11816,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-9　性・年齢調整済み認定率の推移（要介護度の区分別）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：折れ線／掲載箇所：第2章 2-3／単位：%　　出典：地域包括ケア「見える化」システム（B5-a・B6-a・B6-b／注目する地域のみ）　　注：性・年齢調整済み認定率は、全国の人口構成に合わせて年齢構成の違いを取り除いた認定率。要介護2以上は国の評価指標の成果指標にあたる。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -11741,135 +11865,135 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>令和2年3月末</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>19.5</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>12.8</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>10.4</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>6.7</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>令和3年3月末</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>20.3</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>13.5</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>10.3</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="15" t="n">
         <v>6.8</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>令和4年3月末</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>20.7</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>14.3</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>9.9</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="15" t="n">
         <v>6.4</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>令和5年3月末</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>21.3</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>14.7</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="15" t="n">
         <v>6.5</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>令和6年3月末</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>22.1</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>16.4</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="15" t="n">
         <v>5.7</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>令和7年3月末</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>21.6</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>15.4</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="15" t="n">
         <v>6.2</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>令和8年3月末</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>16.5</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="15" t="n">
         <v>6.6</v>
       </c>
     </row>
@@ -11899,21 +12023,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-1　年齢階級別人口の比較（平成22年・令和7年）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：横棒／掲載箇所：第2章 2-1／単位：人　　出典：総務省「国勢調査」、国立社会保障・人口問題研究所「日本の地域別将来推計人口」</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -11938,67 +12062,67 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>15歳未満</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>415</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>186</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>15〜39歳</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>713</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>451</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>40〜64歳</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>1166</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>741</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>65〜74歳</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>345</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>457</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>75歳以上</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>546</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>480</v>
       </c>
     </row>
@@ -12029,21 +12153,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-2　高齢化率の推移と将来推計（村・福島県・全国）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：折れ線／掲載箇所：第2章 2-1／単位：%　　出典：地域包括ケア「見える化」システム</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -12073,146 +12197,146 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>2010年</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>24.9</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>22.8</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>2015年</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>31.8</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>28.3</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>26.3</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>2020年</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>37.1</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>31.2</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>2025年</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>40.5</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>34.2</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>29.6</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>2030年</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>43.9</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>36.1</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>30.8</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>2035年</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>45.2</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>37.7</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>32.3</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>2040年</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>46.3</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>40.3</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>34.8</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>2045年</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>47.8</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>42.5</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <v>36.3</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>2050年</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>49.2</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>44.2</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="15" t="n">
         <v>37.1</v>
       </c>
     </row>
@@ -12244,21 +12368,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>図2-3　将来推計人口（年齢3区分）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>種類：積上げ棒／掲載箇所：第2章 2-2／単位：人　　出典：国立社会保障・人口問題研究所「日本の地域別将来推計人口」</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>黄色の数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。空欄は「まだ入っていない」ことを表し、0 とは意味が違います。</t>
         </is>
@@ -12293,173 +12417,173 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>2010年</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>415</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <v>1879</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="15" t="n">
         <v>891</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>3185</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>2015年</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>324</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>1608</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="15" t="n">
         <v>899</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="15" t="n">
         <v>2831</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>2020年</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>258</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>1349</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="15" t="n">
         <v>948</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="15" t="n">
         <v>2556</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>2025年</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>186</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>1192</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>937</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="15" t="n">
         <v>2315</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>2030年</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>156</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>1008</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <v>911</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="15" t="n">
         <v>2075</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>2035年</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>132</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>888</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <v>843</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="15" t="n">
         <v>1863</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>2040年</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>119</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>770</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <v>765</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="15" t="n">
         <v>1654</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>2045年</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>104</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>651</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <v>692</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="15" t="n">
         <v>1447</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>2050年</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>554</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="15" t="n">
         <v>619</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="15" t="n">
         <v>1259</v>
       </c>
     </row>

--- a/output/11_北塩原村第10期_図表データ管理台帳.xlsx
+++ b/output/11_北塩原村第10期_図表データ管理台帳.xlsx
@@ -1,39 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_この表について" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_図表台帳" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_素案の表との突合" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_交付金との紐付け" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_資8の一覧との突合" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="D_fig2-21_調整済み認定率" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="D_fig2-1_人口構成比較" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="D_fig2-2_高齢化率推移" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="D_fig2-3_将来推計人口" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="D_fig2-4_前期後期高齢者" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="D_fig2-5_認定率推移" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="D_fig2-6_要介護度別認定者数" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="D_fig2-7_要支援1" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="D_fig2-8_新規認定要支援1" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="D_fig2-9_1人あたり費用額" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="D_fig2-10_費用額内訳" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="D_fig2-11_在宅施設別給付月額" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="D_fig2-14_サービス区分別変化" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="D_fig2-12_1人あたり定員" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="D_fig2-13_地域支援事業費" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="D_fig2-20_通いの場" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="D_fig2-15_財政指数" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="D_fig2-16_保険料比較" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="D_fig2-17_保険料と必要額" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="D_fig2-18_交付金指標群" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="D_fig2-19_交付金得点推移" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="99_自己点検" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_この表について" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_図表台帳" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_素案の表との突合" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_交付金との紐付け" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_資8の一覧との突合" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-21_調整済み認定率" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-1_人口構成比較" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-2_高齢化率推移" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-3_将来推計人口" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-4_前期後期高齢者" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-5_認定率推移" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-6_要介護度別認定者数" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-7_要支援1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-8_新規認定要支援1" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-9_1人あたり費用額" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-10_費用額内訳" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-11_在宅施設別給付月額" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-14_サービス区分別変化" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-12_1人あたり定員" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-13_地域支援事業費" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-20_通いの場" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-15_財政指数" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-16_保険料比較" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-17_保険料と必要額" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-18_交付金指標群" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-19_交付金得点推移" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -272,14 +272,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -302,14 +302,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -334,14 +334,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -366,14 +366,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -398,14 +398,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -457,14 +457,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -487,26 +487,26 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$14</f>
+              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$B$6:$B$14</f>
+              <f>'D_fig2-9_1人あたり費用額'!$B$6:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -519,26 +519,26 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$14</f>
+              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$C$6:$C$14</f>
+              <f>'D_fig2-9_1人あたり費用額'!$C$6:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -551,26 +551,26 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$14</f>
+              <f>'D_fig2-9_1人あたり費用額'!$A$6:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'D_fig2-9_1人あたり費用額'!$D$6:$D$14</f>
+              <f>'D_fig2-9_1人あたり費用額'!$D$6:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -610,14 +610,14 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -641,7 +641,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -665,7 +665,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -689,7 +689,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -742,14 +742,14 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -772,14 +772,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -804,14 +804,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -863,14 +863,14 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -894,7 +894,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -918,7 +918,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -970,14 +970,14 @@
 </file>
 
 <file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1000,14 +1000,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1032,14 +1032,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1091,14 +1091,14 @@
 </file>
 
 <file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1122,7 +1122,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1146,7 +1146,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1170,7 +1170,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1194,7 +1194,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1247,14 +1247,14 @@
 </file>
 
 <file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1278,7 +1278,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1330,14 +1330,14 @@
 </file>
 
 <file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1360,14 +1360,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1392,14 +1392,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1424,14 +1424,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1483,14 +1483,14 @@
 </file>
 
 <file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1514,7 +1514,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1538,7 +1538,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1562,7 +1562,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1614,14 +1614,14 @@
 </file>
 
 <file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1644,14 +1644,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1676,14 +1676,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1735,14 +1735,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1766,7 +1766,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1790,7 +1790,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1842,14 +1842,14 @@
 </file>
 
 <file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1873,7 +1873,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1897,7 +1897,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1949,14 +1949,14 @@
 </file>
 
 <file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1979,14 +1979,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2011,14 +2011,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2043,14 +2043,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2102,14 +2102,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2132,14 +2132,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2164,14 +2164,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2196,14 +2196,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2255,14 +2255,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2286,7 +2286,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2310,7 +2310,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2334,7 +2334,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2358,7 +2358,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2411,14 +2411,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2442,7 +2442,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2466,7 +2466,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2519,14 +2519,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2549,14 +2549,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2581,14 +2581,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2613,14 +2613,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2672,14 +2672,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2703,7 +2703,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2727,7 +2727,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2751,7 +2751,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2775,7 +2775,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2799,7 +2799,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2823,7 +2823,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2847,7 +2847,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2900,14 +2900,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2931,7 +2931,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2983,14 +2983,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3014,7 +3014,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -3066,7 +3066,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -3081,9 +3081,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3093,7 +3093,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -3108,9 +3108,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3120,7 +3120,7 @@
 </file>
 
 <file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -3135,9 +3135,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3147,7 +3147,7 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -3162,9 +3162,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3174,7 +3174,7 @@
 </file>
 
 <file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -3189,9 +3189,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3201,7 +3201,7 @@
 </file>
 
 <file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -3216,9 +3216,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3228,7 +3228,7 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -3243,9 +3243,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3255,7 +3255,7 @@
 </file>
 
 <file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -3270,9 +3270,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3282,7 +3282,7 @@
 </file>
 
 <file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -3297,9 +3297,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3309,7 +3309,7 @@
 </file>
 
 <file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -3324,9 +3324,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3336,7 +3336,7 @@
 </file>
 
 <file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -3351,9 +3351,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3363,7 +3363,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -3378,9 +3378,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3390,7 +3390,7 @@
 </file>
 
 <file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -3405,9 +3405,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3417,7 +3417,7 @@
 </file>
 
 <file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -3432,9 +3432,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3444,7 +3444,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -3459,9 +3459,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3471,7 +3471,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -3486,9 +3486,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3498,7 +3498,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -3513,9 +3513,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3525,7 +3525,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -3540,9 +3540,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3552,7 +3552,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -3567,9 +3567,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3579,7 +3579,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -3594,9 +3594,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3606,7 +3606,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -3621,9 +3621,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4996,7 +4996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5015,7 +5015,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>種類：折れ線／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム</t>
+          <t>種類：折れ線／掲載箇所：第2章 2-4／単位：円　　出典：地域包括ケア「見える化」システム（P3 介護費用額の推移。平成30年度からの収録）</t>
         </is>
       </c>
     </row>
@@ -5052,144 +5052,128 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>平成29年度</t>
+          <t>平成30年度</t>
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>25039</v>
+        <v>25606</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>24056</v>
+        <v>24449</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>23238</v>
+        <v>23499</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>平成30年度</t>
+          <t>令和元年度</t>
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>25606</v>
+        <v>23624</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>24449</v>
+        <v>24819</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>23499</v>
+        <v>24106</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>令和元年度</t>
+          <t>令和2年度</t>
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>23624</v>
+        <v>22072</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>24819</v>
+        <v>25213</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>24106</v>
+        <v>24567</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>令和2年度</t>
+          <t>令和3年度</t>
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>22072</v>
+        <v>21041</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>25213</v>
+        <v>25426</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>24567</v>
+        <v>25137</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>令和3年度</t>
+          <t>令和4年度</t>
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>21041</v>
+        <v>21563</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>25426</v>
+        <v>25477</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>25137</v>
+        <v>25471</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>令和4年度</t>
+          <t>令和5年度</t>
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>21563</v>
+        <v>23008</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>25477</v>
+        <v>25871</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>25471</v>
+        <v>26229</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>令和5年度</t>
+          <t>令和6年度</t>
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>23008</v>
+        <v>22751</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>25871</v>
+        <v>26518</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>26229</v>
+        <v>27147</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>令和6年度</t>
+          <t>令和7年度</t>
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>22751</v>
+        <v>24696</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>26518</v>
+        <v>26848</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>27147</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>令和7年度</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>24696</v>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>26848</v>
-      </c>
-      <c r="D14" s="15" t="n">
         <v>27815</v>
       </c>
     </row>
@@ -6421,7 +6405,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>3</v>

--- a/output/11_北塩原村第10期_図表データ管理台帳.xlsx
+++ b/output/11_北塩原村第10期_図表データ管理台帳.xlsx
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>算定上の保険料月額と条例上の基準額</t>
+          <t>参考　当方の検算による保険料月額の12パターンと条例上の基準額</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>本計画の算定による</t>
+          <t>当方の検算（令和5年度決算を基礎とした算定）による</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>算定上の保険料月額と条例上の基準額</t>
+          <t>参考　当方の検算による保険料月額の12パターンと条例上の基準額</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">

--- a/output/11_北塩原村第10期_図表データ管理台帳.xlsx
+++ b/output/11_北塩原村第10期_図表データ管理台帳.xlsx
@@ -8416,12 +8416,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>existing - registered == 空</t>
+          <t>existing - registered == 空（単色版はもとの図が登録済み）</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>余り0件</t>
+          <t>余り0件・もとの図が無い単色版0件</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">

--- a/output/11_北塩原村第10期_図表データ管理台帳.xlsx
+++ b/output/11_北塩原村第10期_図表データ管理台帳.xlsx
@@ -1374,12 +1374,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'D_fig2-15_財政指数'!$A$6:$A$15</f>
+              <f>'D_fig2-15_財政指数'!$A$6:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'D_fig2-15_財政指数'!$B$6:$B$15</f>
+              <f>'D_fig2-15_財政指数'!$B$6:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -1406,12 +1406,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'D_fig2-15_財政指数'!$A$6:$A$15</f>
+              <f>'D_fig2-15_財政指数'!$A$6:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'D_fig2-15_財政指数'!$C$6:$C$15</f>
+              <f>'D_fig2-15_財政指数'!$C$6:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -1438,12 +1438,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'D_fig2-15_財政指数'!$A$6:$A$15</f>
+              <f>'D_fig2-15_財政指数'!$A$6:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'D_fig2-15_財政指数'!$D$6:$D$15</f>
+              <f>'D_fig2-15_財政指数'!$D$6:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>3</v>
@@ -7502,7 +7502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7713,6 +7713,22 @@
       </c>
       <c r="D15" s="15" t="n">
         <v>69539</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>R6年度</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>278693</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>39865</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>75452</v>
       </c>
     </row>
   </sheetData>
